--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/IDAHO_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/IDAHO_2015.xlsx
@@ -3426,7 +3426,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C171">
@@ -6079,7 +6079,7 @@
         <v>46</v>
       </c>
       <c r="D318">
-        <v>0.009484536082474227</v>
+        <v>0.009484536082474229</v>
       </c>
     </row>
     <row r="319">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C502">
